--- a/docs/templates/import-akaun-penternak-pembekal.xlsx
+++ b/docs/templates/import-akaun-penternak-pembekal.xlsx
@@ -8,7 +8,7 @@
     <sheet name="Senarai" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Peranan">Senarai!$A$2:$A$3</definedName>
+    <definedName name="JenisRantaian">Senarai!$A$2:$A$5</definedName>
     <definedName name="Negeri">Senarai!$B$2:$B$17</definedName>
     <definedName name="PilihNegeri">Senarai!$S$2</definedName>
     <definedName name="Johor">Senarai!$C$2:$C$11</definedName>
@@ -89,23 +89,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1" style="2"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1" style="2"/>
-    <col min="12" max="12" width="16" customWidth="1" style="2"/>
-    <col min="13" max="13" width="32" customWidth="1"/>
-    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="42" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1" style="2"/>
+    <col min="13" max="13" width="16" customWidth="1" style="2"/>
+    <col min="14" max="14" width="32" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -131,66 +132,71 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peranan *</t>
+          <t xml:space="preserve">Jenis dalam rantaian *</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nama lapisan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">No. Pendaftaran *</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nama Syarikat / Ladang *</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Alamat *</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Negeri</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Daerah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Poskod</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No. Telefon</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Emel Syarikat</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Laman Web</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Peranan" prompt="Pilih Pembekal atau Penternak." errorTitle="Peranan" error="Pilih Pembekal atau Penternak dari senarai." sqref="E2:E500">
-      <formula1>Peranan</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Jenis dalam rantaian" prompt="Pilih Pengeluar, Pemborong, Peruncit, atau Lain-lain. Consumer tidak diisi di sini." errorTitle="Jenis dalam rantaian" error="Pilih jenis dari senarai." sqref="E2:E500">
+      <formula1>JenisRantaian</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Negeri" prompt="Pilih negeri atau wilayah persekutuan." errorTitle="Negeri" error="Pilih negeri dari senarai." sqref="I2:I500">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Negeri" prompt="Pilih negeri atau wilayah persekutuan." errorTitle="Negeri" error="Pilih negeri dari senarai." sqref="J2:J500">
       <formula1>Negeri</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Daerah" prompt="Pilih negeri pada baris ini dahulu. Senarai daerah mengikut negeri itu." errorTitle="Daerah" error="Pilih daerah dari senarai negeri ini." sqref="J2:J500">
-      <formula1>IF(I2="",PilihNegeri,INDIRECT(SUBSTITUTE(I2," ","_")))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Daerah" prompt="Pilih negeri pada baris ini dahulu. Senarai daerah mengikut negeri itu." errorTitle="Daerah" error="Pilih daerah dari senarai negeri ini." sqref="K2:K500">
+      <formula1>IF(J2="",PilihNegeri,INDIRECT(SUBSTITUTE(J2," ","_")))</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -198,23 +204,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1" style="2"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1" style="2"/>
-    <col min="12" max="12" width="16" customWidth="1" style="2"/>
-    <col min="13" max="13" width="32" customWidth="1"/>
-    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="42" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1" style="2"/>
+    <col min="13" max="13" width="16" customWidth="1" style="2"/>
+    <col min="14" max="14" width="32" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -240,50 +247,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peranan *</t>
+          <t xml:space="preserve">Jenis dalam rantaian *</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nama lapisan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">No. Pendaftaran *</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nama Syarikat / Ladang *</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Alamat *</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Negeri</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Daerah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Poskod</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No. Telefon</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Emel Syarikat</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Laman Web</t>
         </is>
@@ -302,7 +314,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ahmad.penternak@example.com</t>
+          <t xml:space="preserve">ahmad.ladang@example.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -312,61 +324,62 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penternak</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+          <t xml:space="preserve">Pengeluar</t>
+        </is>
+      </c>
+      <c r="F2"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">PTN-0001</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ladang Lembu Ahmad</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">Lot 12, Jalan Ladang, Pontian</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">Johor</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pontian</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">82000</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">012-3456789</t>
         </is>
       </c>
-      <c r="M2"/>
       <c r="N2"/>
+      <c r="O2"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siti binti Omar</t>
+          <t xml:space="preserve">Nora binti Karim</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850202026666</t>
+          <t xml:space="preserve">810202026666</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">siti.pembekal@example.com</t>
+          <t xml:space="preserve">nora.borong@example.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -376,61 +389,127 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pembekal</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PMB-0001</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Pemborong</t>
+        </is>
+      </c>
+      <c r="F3"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pembekal Buah Siti</t>
+          <t xml:space="preserve">PBR-0001</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8, Jalan Pasar, Klang</t>
+          <t xml:space="preserve">Borong Buah Nora</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve">20, Jalan Gudang, Klang</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Selangor</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Klang</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">41000</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">019-1112223</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siti@example.com</t>
-        </is>
-      </c>
-      <c r="N3"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nora@example.com</t>
+        </is>
+      </c>
+      <c r="O3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aina binti Rahim</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820303037777</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aina.runcit@example.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tukar123!</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peruncit</t>
+        </is>
+      </c>
+      <c r="F4"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RNC-0001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runcit Segar Aina</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8, Jalan Pasar, Melaka</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Melaka</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Melaka Tengah</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75000</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">012-8887766</t>
+        </is>
+      </c>
+      <c r="N4"/>
+      <c r="O4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Peranan" prompt="Pilih Pembekal atau Penternak." errorTitle="Peranan" error="Pilih Pembekal atau Penternak dari senarai." sqref="E2:E20">
-      <formula1>Peranan</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Jenis dalam rantaian" prompt="Pilih Pengeluar, Pemborong, Peruncit, atau Lain-lain. Consumer tidak diisi di sini." errorTitle="Jenis dalam rantaian" error="Pilih jenis dari senarai." sqref="E2:E20">
+      <formula1>JenisRantaian</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Negeri" prompt="Pilih negeri atau wilayah persekutuan." errorTitle="Negeri" error="Pilih negeri dari senarai." sqref="I2:I20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Negeri" prompt="Pilih negeri atau wilayah persekutuan." errorTitle="Negeri" error="Pilih negeri dari senarai." sqref="J2:J20">
       <formula1>Negeri</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Daerah" prompt="Pilih negeri pada baris ini dahulu. Senarai daerah mengikut negeri itu." errorTitle="Daerah" error="Pilih daerah dari senarai negeri ini." sqref="J2:J20">
-      <formula1>IF(I2="",PilihNegeri,INDIRECT(SUBSTITUTE(I2," ","_")))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Daerah" prompt="Pilih negeri pada baris ini dahulu. Senarai daerah mengikut negeri itu." errorTitle="Daerah" error="Pilih daerah dari senarai negeri ini." sqref="K2:K20">
+      <formula1>IF(J2="",PilihNegeri,INDIRECT(SUBSTITUTE(J2," ","_")))</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -438,18 +517,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="88" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="108" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Import akaun Penternak / Pembekal — Sistem Jejak GPL</t>
+          <t xml:space="preserve">Import akaun syarikat — Sistem Jejak GPL</t>
         </is>
       </c>
     </row>
@@ -466,89 +545,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lajur Peranan, Negeri dan Daerah ada senarai pilihan pada setiap baris. Klik anak panah di dalam sel.</t>
+          <t xml:space="preserve">Jenis dalam rantaian sama dengan Profil → Jenis dalam rantaian. Jejak pecahan guna jenis syarikat yang memegang lot itu.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilih Negeri dahulu. Senarai Daerah pada baris itu berubah mengikut negeri. Jika negeri ditukar, pilih semula daerah.</t>
+          <t xml:space="preserve">Jenis dalam rantaian, Negeri dan Daerah ada senarai pilihan pada setiap baris. Klik anak panah di dalam sel.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perlis, Kuala Lumpur, Labuan dan Putrajaya hanya mempunyai satu pilihan daerah.</t>
+          <t xml:space="preserve">Pilih Negeri dahulu. Senarai Daerah pada baris itu berubah mengikut negeri. Jika negeri ditukar, pilih semula daerah.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Perlis, Kuala Lumpur, Labuan dan Putrajaya hanya mempunyai satu pilihan daerah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consumer bukan jenis akaun. Jejak menambah Consumer sendiri bila lot dijual tanpa log masuk syarikat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Padam baris contoh sebelum guna data sebenar. Jangan hantar fail ini melalui emel kerana ia mengandungi kata laluan.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Lajur</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Wajib</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Peraturan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nama Pengguna</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ya</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nama orang yang log masuk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No. Kad Pengenalan</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ya</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 digit tanpa sengkang. Lajur ini disimpan sebagai teks.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emel Log Masuk</t>
+          <t xml:space="preserve">Nama Pengguna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -558,14 +617,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emel unik untuk log masuk. Peranan dalaman akaun ialah Usahawan.</t>
+          <t xml:space="preserve">Nama orang yang log masuk.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kata Laluan</t>
+          <t xml:space="preserve">No. Kad Pengenalan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -575,14 +634,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minimum 8 aksara. Minta pengguna tukar selepas log masuk pertama.</t>
+          <t xml:space="preserve">12 digit tanpa sengkang. Lajur ini disimpan sebagai teks.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peranan</t>
+          <t xml:space="preserve">Emel Log Masuk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -592,14 +651,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dropdown: Pembekal atau Penternak.</t>
+          <t xml:space="preserve">Emel unik untuk log masuk. Peranan dalaman akaun ialah Usahawan.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. Pendaftaran</t>
+          <t xml:space="preserve">Kata Laluan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -609,14 +668,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unik. Nombor akaun luaran dijana sebagai FAMA-&lt;no. pendaftaran&gt;.</t>
+          <t xml:space="preserve">Minimum 8 aksara. Minta pengguna tukar selepas log masuk pertama.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nama Syarikat / Ladang</t>
+          <t xml:space="preserve">Jenis dalam rantaian</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -626,82 +685,82 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nama yang dipaparkan pada syarikat.</t>
+          <t xml:space="preserve">Dropdown: Pengeluar, Pemborong, Peruncit, atau Lain-lain.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alamat</t>
+          <t xml:space="preserve">Nama lapisan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya</t>
+          <t xml:space="preserve">Jika Lain-lain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alamat premis atau ladang.</t>
+          <t xml:space="preserve">Wajib bila jenis ialah Lain-lain. Contoh: Penternak atau Pengumpul. Teks ini yang keluar pada jejak.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negeri</t>
+          <t xml:space="preserve">No. Pendaftaran</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tidak</t>
+          <t xml:space="preserve">Ya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dropdown negeri dan wilayah persekutuan.</t>
+          <t xml:space="preserve">Unik. Nombor akaun luaran dijana sebagai FAMA-&lt;no. pendaftaran&gt;.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daerah</t>
+          <t xml:space="preserve">Nama Syarikat / Ladang</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tidak</t>
+          <t xml:space="preserve">Ya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dropdown mengikut negeri pada baris yang sama.</t>
+          <t xml:space="preserve">Nama yang dipaparkan pada syarikat.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poskod</t>
+          <t xml:space="preserve">Alamat</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tidak</t>
+          <t xml:space="preserve">Ya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disimpan sebagai teks supaya sifar di hadapan kekal.</t>
+          <t xml:space="preserve">Alamat premis atau ladang.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. Telefon</t>
+          <t xml:space="preserve">Negeri</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -711,14 +770,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombor telefon syarikat.</t>
+          <t xml:space="preserve">Dropdown negeri dan wilayah persekutuan.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emel Syarikat</t>
+          <t xml:space="preserve">Daerah</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -728,14 +787,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jika kosong, emel log masuk digunakan untuk syarikat.</t>
+          <t xml:space="preserve">Dropdown mengikut negeri pada baris yang sama.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laman Web</t>
+          <t xml:space="preserve">Poskod</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -745,56 +804,173 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilihan. Contoh: https://ladang.example</t>
+          <t xml:space="preserve">Disimpan sebagai teks supaya sifar di hadapan kekal.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peranan dalam fail</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lapisan syarikat dalam sistem</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. Telefon</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tidak</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nombor telefon syarikat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emel Syarikat</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tidak</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jika kosong, emel log masuk digunakan untuk syarikat.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pembekal</t>
+          <t xml:space="preserve">Laman Web</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUPPLIER — label paparan: Pembekal</t>
+          <t xml:space="preserve">Tidak</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilihan. Contoh: https://ladang.example</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Penternak</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTHER — label paparan: Penternak</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28"/>
+      <c r="A27"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jenis dalam fail</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kod sistem</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paparan pada jejak</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contoh baris ada pada helaian Contoh. Kedua-dua baris contoh juga ada dropdown.</t>
+          <t xml:space="preserve">Pengeluar</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPPLIER</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pengeluar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pemborong</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXPORTER</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pemborong</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peruncit</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAILER</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peruncit</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lain-lain</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTHER</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nama lapisan, contoh Penternak</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consumer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bukan akaun. Ditambah bila lot dijual tanpa syarikat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contoh pada helaian Contoh: Pengeluar, Pemborong, dan Peruncit. Tiada baris Consumer.</t>
         </is>
       </c>
     </row>
@@ -807,31 +983,31 @@
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="19" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peranan</t>
+          <t xml:space="preserve">Jenis</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -924,7 +1100,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pembekal</t>
+          <t xml:space="preserve">Pengeluar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1021,7 +1197,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penternak</t>
+          <t xml:space="preserve">Pemborong</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1096,7 +1272,11 @@
       <c r="S3"/>
     </row>
     <row r="4">
-      <c r="A4"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peruncit</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">Kelantan</t>
@@ -1169,7 +1349,11 @@
       <c r="S4"/>
     </row>
     <row r="5">
-      <c r="A5"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lain-lain</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t xml:space="preserve">Melaka</t>
